--- a/docs/scenario-template.xlsx
+++ b/docs/scenario-template.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -86,6 +86,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -799,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -911,6 +912,11 @@
       <c r="R1" s="3" t="inlineStr">
         <is>
           <t>ヒント（English）</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>入れる条件（満たすまで地図には出るが入れない）</t>
         </is>
       </c>
     </row>
